--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,20 +468,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>814560106</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1163972931</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1163972931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -493,6 +487,60 @@
           <t xml:space="preserve">Locator.click: Timeout 30000ms exceeded.
 Call log:
   - waiting for get_by_role("button", name="Tải ảnh lên").first
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
+Call log:
+  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>814560106</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1163972931</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
+Call log:
+  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "networkidle"
 </t>
         </is>
       </c>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,20 +516,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>814560106</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1163972931</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1163972931</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -542,6 +536,33 @@
 Call log:
   - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "networkidle"
 </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>814560106</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1163972931</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No file input found</t>
         </is>
       </c>
     </row>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -540,29 +540,113 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No file input found</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>814560106</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>1163972931</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>No file input found</t>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
         </is>
       </c>
     </row>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,27 +624,156 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
+Call log:
+  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "domcontentloaded"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>814560106</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>1163972931</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>ĐĂNG NHẬP</t>
         </is>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,29 +753,53 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>814560106</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>1163972931</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ĐĂNG NHẬP</t>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
+Call log:
+  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "domcontentloaded"
+</t>
         </is>
       </c>
     </row>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,20 +774,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>814560106</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1163972931</t>
-        </is>
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1163972931</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -803,6 +797,33 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>814560106</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1163972931</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,29 +798,53 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>814560106</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>1163972931</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ĐĂNG NHẬP</t>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
+Call log:
+  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "domcontentloaded"
+</t>
         </is>
       </c>
     </row>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,20 +819,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>814560106</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1163972931</t>
-        </is>
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1163972931</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -848,6 +842,36 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>814560106</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1163972931</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
+Call log:
+  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "domcontentloaded"
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,16 @@
           <t>message</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ngay_cap</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>noi_cap</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -466,6 +476,8 @@
 </t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -490,6 +502,8 @@
 </t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -514,6 +528,8 @@
 </t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -538,6 +554,8 @@
 </t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -559,6 +577,8 @@
           <t>No file input found</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -580,6 +600,8 @@
           <t>ĐĂNG NHẬP</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -601,6 +623,8 @@
           <t>ĐĂNG NHẬP</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -622,6 +646,8 @@
           <t>ĐĂNG NHẬP</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -643,6 +669,8 @@
           <t>ĐĂNG NHẬP</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -664,6 +692,8 @@
           <t>ĐĂNG NHẬP</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -685,6 +715,8 @@
           <t>ĐĂNG NHẬP</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -706,6 +738,8 @@
           <t>ĐĂNG NHẬP</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -727,6 +761,8 @@
           <t>ĐĂNG NHẬP</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -751,6 +787,8 @@
 </t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -772,6 +810,8 @@
           <t>ĐĂNG NHẬP</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -796,6 +836,8 @@
 </t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -817,6 +859,8 @@
           <t>ĐĂNG NHẬP</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -841,22 +885,18 @@
 </t>
         </is>
       </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>814560106</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1163972931</t>
-        </is>
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1163972931</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -871,6 +911,112 @@
 </t>
         </is>
       </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
+Call log:
+  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "domcontentloaded"
+</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>814560106</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1163972931</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
+Call log:
+  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "domcontentloaded"
+</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,20 +987,14 @@
       <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>814560106</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1163972931</t>
-        </is>
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1163972931</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1018,6 +1012,328 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
+Call log:
+  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "domcontentloaded"
+</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>23/05/2019</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>GUWAHATI</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Page.wait_for_timeout: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>23/05/2019</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>GUWAHATI</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>23/05/2019</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>GUWAHATI</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Page.wait_for_timeout: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>23/05/2019</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>GUWAHATI</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
+Call log:
+  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "domcontentloaded"
+</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>23/05/2019</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>GUWAHATI</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>'PlaywrightRunner' object has no attribute '_wait_and_finish_face_verification'</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>23/05/2019</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>GUWAHATI</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>'PlaywrightRunner' object has no attribute '_wait_and_finish_face_verification'</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>23/05/2019</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>GUWAHATI</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>'PlaywrightRunner' object has no attribute '_wait_and_finish_face_verification'</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>23/05/2019</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>GUWAHATI</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>23/05/2019</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>GUWAHATI</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>814560106</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1163972931</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>23/05/2019</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>GUWAHATI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,39 +485,225 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>814560106</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>1163972931</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Thiếu Ảnh Hộ chiếu</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>23/05/2019</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>GUWAHATI</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
         </is>
       </c>
     </row>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,37 +671,564 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Page.query_selector_all: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Không thể kết nối tới máy chủ do hệ thống đang bận. Vui lòng thử lại!</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>814560106</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>1163972931</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>RANCHI</t>
         </is>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1198,37 +1198,502 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP - LIÊN HỆ - Vietnamese - TRANG CHỦ - HOÀN THIỆN THÔNG TIN THUÊ BAO - HỖ TRỢ ĐẠI LÝ - CÂU HỎI THƯỜNG GẶP - Mạng di động nhanh nhất Việt Nam, hỗ trợ mạng 5G - Phủ sóng 63/63 tỉnh thành - Liên kết mạng (chuyển vùng quốc tế) với 177 Quốc gia trên khắp thế giới - Data dung lượng lớn, Miễn phí gọi trong nước - Đa dạng lựa chọn với giá cước du lịch hấp dẫn - Hỗ trợ eSim, phát Hotspot cùng nhiều tiện ích khác - English - Vietnam - XÁC THỰC KHUÔN MẶT - Bước 2/3 - Giữ vững khuôn mặt - Hướng dẫn - CÂU HỎI THƯỜNG GẶP - Chào chưa? - Xin Chào Việt Nam - ĐĂNG KÝ - ĐẠI LÝ SIM DU LỊCH - Bạn muốn trở thành đại lý sim du lịch của Vinaphone. Hãy để lại thông tin của bạn dưới đây, chúng tôi sẽ liên hệ với bạn sớm nhất. - Họ và Tên * - Email * - Số điện thoại * - Địa chỉ * - Đăng ký - TIN TỨC - hello việt nam - Xem tiếp - Tieu de - Xem tiếp - Khám Phá Những Lợi Ích Vượt Trội Khi Sử Dụng SIM Du Lịch Của VinaPhone - Xem tiếp - Tiêu đề - Xem tiếp - VinaPhone Chính Thức Ra Mắt Dự Án SIM Du Lịch Đáp Ứng Nhu Cầu Của Du Khách Quốc Tế - Xem tiếp - Xem thêm - Theo dõi chúng tôi - VNPT VinaPhone © 2019. - Giấy phép số: 62/GP-TTĐT do Bộ Thông tin - Truyền thông cấp ngày 09/04/2019. - Tập đoàn Bưu chính Viễn thông Việt Nam - Trụ sở: Tòa nhà VNPT, số 57 Phố Huỳnh Thúc Kháng, Phường Láng Hạ, Quận Đống Đa, Thành phố Hà Nội, Việt Nam - Mã số doanh nghiệp: 0100684378 do Sở Kế hoạch và Đầu tư TP.Hà Nội cấp ngày 22/10/2018 - Giấy phép cung cấp dịch vụ viễn thông số 469/GP-BTTTT do Bộ Thông tin và Truyền thông cấp ngày 14/10/2016 - Giấy phép cung cấp dịch vụ viễn thông số 18/GP-CVT do Bộ Thông tin và Truyền thông cấp ngày 18/01/2018</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP - LIÊN HỆ - Vietnamese - TRANG CHỦ - HOÀN THIỆN THÔNG TIN THUÊ BAO - HỖ TRỢ ĐẠI LÝ - CÂU HỎI THƯỜNG GẶP - Mạng di động nhanh nhất Việt Nam, hỗ trợ mạng 5G - Phủ sóng 63/63 tỉnh thành - Liên kết mạng (chuyển vùng quốc tế) với 177 Quốc gia trên khắp thế giới - Data dung lượng lớn, Miễn phí gọi trong nước - Đa dạng lựa chọn với giá cước du lịch hấp dẫn - Hỗ trợ eSim, phát Hotspot cùng nhiều tiện ích khác - English - Vietnam - XÁC THỰC KHUÔN MẶT - Bước 2/3 - Gần hơn nữa - Hướng dẫn - CÂU HỎI THƯỜNG GẶP - Chào chưa? - Xin Chào Việt Nam - ĐĂNG KÝ - ĐẠI LÝ SIM DU LỊCH - Bạn muốn trở thành đại lý sim du lịch của Vinaphone. Hãy để lại thông tin của bạn dưới đây, chúng tôi sẽ liên hệ với bạn sớm nhất. - Họ và Tên * - Email * - Số điện thoại * - Địa chỉ * - Đăng ký - TIN TỨC - hello việt nam - Xem tiếp - Tieu de - Xem tiếp - Khám Phá Những Lợi Ích Vượt Trội Khi Sử Dụng SIM Du Lịch Của VinaPhone - Xem tiếp - Tiêu đề - Xem tiếp - VinaPhone Chính Thức Ra Mắt Dự Án SIM Du Lịch Đáp Ứng Nhu Cầu Của Du Khách Quốc Tế - Xem tiếp - Xem thêm - Theo dõi chúng tôi - VNPT VinaPhone © 2019. - Giấy phép số: 62/GP-TTĐT do Bộ Thông tin - Truyền thông cấp ngày 09/04/2019. - Tập đoàn Bưu chính Viễn thông Việt Nam - Trụ sở: Tòa nhà VNPT, số 57 Phố Huỳnh Thúc Kháng, Phường Láng Hạ, Quận Đống Đa, Thành phố Hà Nội, Việt Nam - Mã số doanh nghiệp: 0100684378 do Sở Kế hoạch và Đầu tư TP.Hà Nội cấp ngày 22/10/2018 - Giấy phép cung cấp dịch vụ viễn thông số 469/GP-BTTTT do Bộ Thông tin và Truyền thông cấp ngày 14/10/2016 - Giấy phép cung cấp dịch vụ viễn thông số 18/GP-CVT do Bộ Thông tin và Truyền thông cấp ngày 18/01/2018</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>814560106</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>1163972931</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>RANCHI</t>
         </is>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1663,37 +1663,378 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>814560106</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>1163972931</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP - LIÊN HỆ - Vietnamese - TRANG CHỦ - HOÀN THIỆN THÔNG TIN THUÊ BAO - HỖ TRỢ ĐẠI LÝ - CÂU HỎI THƯỜNG GẶP - Mạng di động nhanh nhất Việt Nam, hỗ trợ mạng 5G - Phủ sóng 63/63 tỉnh thành - Liên kết mạng (chuyển vùng quốc tế) với 177 Quốc gia trên khắp thế giới - Data dung lượng lớn, Miễn phí gọi trong nước - Đa dạng lựa chọn với giá cước du lịch hấp dẫn - Hỗ trợ eSim, phát Hotspot cùng nhiều tiện ích khác - English - Vietnam - XÁC THỰC KHUÔN MẶT - Bước 2/3 - Đảm bảo khuôn mặt vừa khung hình - Hướng dẫn - CÂU HỎI THƯỜNG GẶP - Chào chưa? - Xin Chào Việt Nam - ĐĂNG KÝ - ĐẠI LÝ SIM DU LỊCH - Bạn muốn trở thành đại lý sim du lịch của Vinaphone. Hãy để lại thông tin của bạn dưới đây, chúng tôi sẽ liên hệ với bạn sớm nhất. - Họ và Tên * - Email * - Số điện thoại * - Địa chỉ * - Đăng ký - TIN TỨC - hello việt nam - Xem tiếp - Tieu de - Xem tiếp - Khám Phá Những Lợi Ích Vượt Trội Khi Sử Dụng SIM Du Lịch Của VinaPhone - Xem tiếp - Tiêu đề - Xem tiếp - VinaPhone Chính Thức Ra Mắt Dự Án SIM Du Lịch Đáp Ứng Nhu Cầu Của Du Khách Quốc Tế - Xem tiếp - Xem thêm - Theo dõi chúng tôi - VNPT VinaPhone © 2019. - Giấy phép số: 62/GP-TTĐT do Bộ Thông tin - Truyền thông cấp ngày 09/04/2019. - Tập đoàn Bưu chính Viễn thông Việt Nam - Trụ sở: Tòa nhà VNPT, số 57 Phố Huỳnh Thúc Kháng, Phường Láng Hạ, Quận Đống Đa, Thành phố Hà Nội, Việt Nam - Mã số doanh nghiệp: 0100684378 do Sở Kế hoạch và Đầu tư TP.Hà Nội cấp ngày 22/10/2018 - Giấy phép cung cấp dịch vụ viễn thông số 469/GP-BTTTT do Bộ Thông tin và Truyền thông cấp ngày 14/10/2016 - Giấy phép cung cấp dịch vụ viễn thông số 18/GP-CVT do Bộ Thông tin và Truyền thông cấp ngày 18/01/2018</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>RANCHI</t>
         </is>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2004,37 +2004,843 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP - LIÊN HỆ - Vietnamese - TRANG CHỦ - HOÀN THIỆN THÔNG TIN THUÊ BAO - HỖ TRỢ ĐẠI LÝ - CÂU HỎI THƯỜNG GẶP - Mạng di động nhanh nhất Việt Nam, hỗ trợ mạng 5G - Phủ sóng 63/63 tỉnh thành - Liên kết mạng (chuyển vùng quốc tế) với 177 Quốc gia trên khắp thế giới - Data dung lượng lớn, Miễn phí gọi trong nước - Đa dạng lựa chọn với giá cước du lịch hấp dẫn - Hỗ trợ eSim, phát Hotspot cùng nhiều tiện ích khác - English - Vietnam - XÁC THỰC KHUÔN MẶT - Bước 2/3 - Đảm bảo khuôn mặt vừa khung hình - Hướng dẫn - CÂU HỎI THƯỜNG GẶP - Chào chưa? - Xin Chào Việt Nam - ĐĂNG KÝ - ĐẠI LÝ SIM DU LỊCH - Bạn muốn trở thành đại lý sim du lịch của Vinaphone. Hãy để lại thông tin của bạn dưới đây, chúng tôi sẽ liên hệ với bạn sớm nhất. - Họ và Tên * - Email * - Số điện thoại * - Địa chỉ * - Đăng ký - TIN TỨC - hello việt nam - Xem tiếp - Tieu de - Xem tiếp - Khám Phá Những Lợi Ích Vượt Trội Khi Sử Dụng SIM Du Lịch Của VinaPhone - Xem tiếp - Tiêu đề - Xem tiếp - VinaPhone Chính Thức Ra Mắt Dự Án SIM Du Lịch Đáp Ứng Nhu Cầu Của Du Khách Quốc Tế - Xem tiếp - Xem thêm - Theo dõi chúng tôi - VNPT VinaPhone © 2019. - Giấy phép số: 62/GP-TTĐT do Bộ Thông tin - Truyền thông cấp ngày 09/04/2019. - Tập đoàn Bưu chính Viễn thông Việt Nam - Trụ sở: Tòa nhà VNPT, số 57 Phố Huỳnh Thúc Kháng, Phường Láng Hạ, Quận Đống Đa, Thành phố Hà Nội, Việt Nam - Mã số doanh nghiệp: 0100684378 do Sở Kế hoạch và Đầu tư TP.Hà Nội cấp ngày 22/10/2018 - Giấy phép cung cấp dịch vụ viễn thông số 469/GP-BTTTT do Bộ Thông tin và Truyền thông cấp ngày 14/10/2016 - Giấy phép cung cấp dịch vụ viễn thông số 18/GP-CVT do Bộ Thông tin và Truyền thông cấp ngày 18/01/2018</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B57" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP - LIÊN HỆ - Vietnamese - TRANG CHỦ - HOÀN THIỆN THÔNG TIN THUÊ BAO - HỖ TRỢ ĐẠI LÝ - CÂU HỎI THƯỜNG GẶP - Mạng di động nhanh nhất Việt Nam, hỗ trợ mạng 5G - Phủ sóng 63/63 tỉnh thành - Liên kết mạng (chuyển vùng quốc tế) với 177 Quốc gia trên khắp thế giới - Data dung lượng lớn, Miễn phí gọi trong nước - Đa dạng lựa chọn với giá cước du lịch hấp dẫn - Hỗ trợ eSim, phát Hotspot cùng nhiều tiện ích khác - English - Vietnam - XÁC THỰC KHUÔN MẶT - Bước 2/3 - Đảm bảo khuôn mặt vừa khung hình - Hướng dẫn - CÂU HỎI THƯỜNG GẶP - Chào chưa? - Xin Chào Việt Nam - ĐĂNG KÝ - ĐẠI LÝ SIM DU LỊCH - Bạn muốn trở thành đại lý sim du lịch của Vinaphone. Hãy để lại thông tin của bạn dưới đây, chúng tôi sẽ liên hệ với bạn sớm nhất. - Họ và Tên * - Email * - Số điện thoại * - Địa chỉ * - Đăng ký - TIN TỨC - hello việt nam - Xem tiếp - Tieu de - Xem tiếp - Khám Phá Những Lợi Ích Vượt Trội Khi Sử Dụng SIM Du Lịch Của VinaPhone - Xem tiếp - Tiêu đề - Xem tiếp - VinaPhone Chính Thức Ra Mắt Dự Án SIM Du Lịch Đáp Ứng Nhu Cầu Của Du Khách Quốc Tế - Xem tiếp - Xem thêm - Theo dõi chúng tôi - VNPT VinaPhone © 2019. - Giấy phép số: 62/GP-TTĐT do Bộ Thông tin - Truyền thông cấp ngày 09/04/2019. - Tập đoàn Bưu chính Viễn thông Việt Nam - Trụ sở: Tòa nhà VNPT, số 57 Phố Huỳnh Thúc Kháng, Phường Láng Hạ, Quận Đống Đa, Thành phố Hà Nội, Việt Nam - Mã số doanh nghiệp: 0100684378 do Sở Kế hoạch và Đầu tư TP.Hà Nội cấp ngày 22/10/2018 - Giấy phép cung cấp dịch vụ viễn thông số 469/GP-BTTTT do Bộ Thông tin và Truyền thông cấp ngày 14/10/2016 - Giấy phép cung cấp dịch vụ viễn thông số 18/GP-CVT do Bộ Thông tin và Truyền thông cấp ngày 18/01/2018</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1</v>
+      </c>
+      <c r="B59" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP - LIÊN HỆ - Vietnamese - TRANG CHỦ - HOÀN THIỆN THÔNG TIN THUÊ BAO - HỖ TRỢ ĐẠI LÝ - CÂU HỎI THƯỜNG GẶP - Mạng di động nhanh nhất Việt Nam, hỗ trợ mạng 5G - Phủ sóng 63/63 tỉnh thành - Liên kết mạng (chuyển vùng quốc tế) với 177 Quốc gia trên khắp thế giới - Data dung lượng lớn, Miễn phí gọi trong nước - Đa dạng lựa chọn với giá cước du lịch hấp dẫn - Hỗ trợ eSim, phát Hotspot cùng nhiều tiện ích khác - English - Vietnam - XÁC THỰC KHUÔN MẶT - Bước 2/3 - Đảm bảo khuôn mặt vừa khung hình - Hướng dẫn - CÂU HỎI THƯỜNG GẶP - Chào chưa? - Xin Chào Việt Nam - ĐĂNG KÝ - ĐẠI LÝ SIM DU LỊCH - Bạn muốn trở thành đại lý sim du lịch của Vinaphone. Hãy để lại thông tin của bạn dưới đây, chúng tôi sẽ liên hệ với bạn sớm nhất. - Họ và Tên * - Email * - Số điện thoại * - Địa chỉ * - Đăng ký - TIN TỨC - hello việt nam - Xem tiếp - Tieu de - Xem tiếp - Khám Phá Những Lợi Ích Vượt Trội Khi Sử Dụng SIM Du Lịch Của VinaPhone - Xem tiếp - Tiêu đề - Xem tiếp - VinaPhone Chính Thức Ra Mắt Dự Án SIM Du Lịch Đáp Ứng Nhu Cầu Của Du Khách Quốc Tế - Xem tiếp - Xem thêm - Theo dõi chúng tôi - VNPT VinaPhone © 2019. - Giấy phép số: 62/GP-TTĐT do Bộ Thông tin - Truyền thông cấp ngày 09/04/2019. - Tập đoàn Bưu chính Viễn thông Việt Nam - Trụ sở: Tòa nhà VNPT, số 57 Phố Huỳnh Thúc Kháng, Phường Láng Hạ, Quận Đống Đa, Thành phố Hà Nội, Việt Nam - Mã số doanh nghiệp: 0100684378 do Sở Kế hoạch và Đầu tư TP.Hà Nội cấp ngày 22/10/2018 - Giấy phép cung cấp dịch vụ viễn thông số 469/GP-BTTTT do Bộ Thông tin và Truyền thông cấp ngày 14/10/2016 - Giấy phép cung cấp dịch vụ viễn thông số 18/GP-CVT do Bộ Thông tin và Truyền thông cấp ngày 18/01/2018</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>1</v>
+      </c>
+      <c r="B61" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1</v>
+      </c>
+      <c r="B64" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1</v>
+      </c>
+      <c r="B65" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1</v>
+      </c>
+      <c r="B66" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1</v>
+      </c>
+      <c r="B74" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1</v>
+      </c>
+      <c r="B75" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1</v>
+      </c>
+      <c r="B77" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>814560106</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>1163972931</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>ĐĂNG NHẬP - LIÊN HỆ - Vietnamese - TRANG CHỦ - HOÀN THIỆN THÔNG TIN THUÊ BAO - HỖ TRỢ ĐẠI LÝ - CÂU HỎI THƯỜNG GẶP - Mạng di động nhanh nhất Việt Nam, hỗ trợ mạng 5G - Phủ sóng 63/63 tỉnh thành - Liên kết mạng (chuyển vùng quốc tế) với 177 Quốc gia trên khắp thế giới - Data dung lượng lớn, Miễn phí gọi trong nước - Đa dạng lựa chọn với giá cước du lịch hấp dẫn - Hỗ trợ eSim, phát Hotspot cùng nhiều tiện ích khác - English - Vietnam - XÁC THỰC KHUÔN MẶT - Bước 2/3 - Đảm bảo khuôn mặt vừa khung hình - Hướng dẫn - CÂU HỎI THƯỜNG GẶP - Chào chưa? - Xin Chào Việt Nam - ĐĂNG KÝ - ĐẠI LÝ SIM DU LỊCH - Bạn muốn trở thành đại lý sim du lịch của Vinaphone. Hãy để lại thông tin của bạn dưới đây, chúng tôi sẽ liên hệ với bạn sớm nhất. - Họ và Tên * - Email * - Số điện thoại * - Địa chỉ * - Đăng ký - TIN TỨC - hello việt nam - Xem tiếp - Tieu de - Xem tiếp - Khám Phá Những Lợi Ích Vượt Trội Khi Sử Dụng SIM Du Lịch Của VinaPhone - Xem tiếp - Tiêu đề - Xem tiếp - VinaPhone Chính Thức Ra Mắt Dự Án SIM Du Lịch Đáp Ứng Nhu Cầu Của Du Khách Quốc Tế - Xem tiếp - Xem thêm - Theo dõi chúng tôi - VNPT VinaPhone © 2019. - Giấy phép số: 62/GP-TTĐT do Bộ Thông tin - Truyền thông cấp ngày 09/04/2019. - Tập đoàn Bưu chính Viễn thông Việt Nam - Trụ sở: Tòa nhà VNPT, số 57 Phố Huỳnh Thúc Kháng, Phường Láng Hạ, Quận Đống Đa, Thành phố Hà Nội, Việt Nam - Mã số doanh nghiệp: 0100684378 do Sở Kế hoạch và Đầu tư TP.Hà Nội cấp ngày 22/10/2018 - Giấy phép cung cấp dịch vụ viễn thông số 469/GP-BTTTT do Bộ Thông tin và Truyền thông cấp ngày 14/10/2016 - Giấy phép cung cấp dịch vụ viễn thông số 18/GP-CVT do Bộ Thông tin và Truyền thông cấp ngày 18/01/2018</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>RANCHI</t>
         </is>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2810,37 +2810,130 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" t="n">
+        <v>1</v>
+      </c>
+      <c r="B78" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1</v>
+      </c>
+      <c r="B79" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B80" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>814560106</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>1163972931</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>RANCHI</t>
         </is>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2903,37 +2903,192 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" t="n">
+        <v>1</v>
+      </c>
+      <c r="B81" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1</v>
+      </c>
+      <c r="B82" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1</v>
+      </c>
+      <c r="B83" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1</v>
+      </c>
+      <c r="B84" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1</v>
+      </c>
+      <c r="B85" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>814560106</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>1163972931</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>RANCHI</t>
         </is>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3058,37 +3058,99 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" t="n">
+        <v>1</v>
+      </c>
+      <c r="B86" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1</v>
+      </c>
+      <c r="B87" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>814560106</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>1163972931</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>RANCHI</t>
         </is>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3120,20 +3120,14 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>814560106</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>1163972931</t>
-        </is>
+      <c r="A88" t="n">
+        <v>1</v>
+      </c>
+      <c r="B88" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1163972931</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3153,6 +3147,1252 @@
       <c r="G88" t="inlineStr">
         <is>
           <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1</v>
+      </c>
+      <c r="B89" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1</v>
+      </c>
+      <c r="B90" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1</v>
+      </c>
+      <c r="B91" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1</v>
+      </c>
+      <c r="B92" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2</v>
+      </c>
+      <c r="B93" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C93" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ministry of Home Affairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1</v>
+      </c>
+      <c r="B94" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="B95" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2</v>
+      </c>
+      <c r="B96" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C96" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP - LIÊN HỆ - Vietnamese - TRANG CHỦ - HOÀN THIỆN THÔNG TIN THUÊ BAO - HỖ TRỢ ĐẠI LÝ - CÂU HỎI THƯỜNG GẶP - Mạng di động nhanh nhất Việt Nam, hỗ trợ mạng 5G - Phủ sóng 63/63 tỉnh thành - Liên kết mạng (chuyển vùng quốc tế) với 177 Quốc gia trên khắp thế giới - Data dung lượng lớn, Miễn phí gọi trong nước - Đa dạng lựa chọn với giá cước du lịch hấp dẫn - Hỗ trợ eSim, phát Hotspot cùng nhiều tiện ích khác - Xác nhận thông tin - Quý khách vui lòng kiểm tra lại các thông tin được ghi nhận như sau: - Họ và Tên* - Giới tính* - Ngày sinh* - Quốc tịch* - Số hộ chiếu* - Ngày hết hạn - Ngày cấp - Nơi cấp - Số điện thoại - Thực hiện lạiXác nhận - CÂU HỎI THƯỜNG GẶP - Chào chưa? - Xin Chào Việt Nam - ĐĂNG KÝ - ĐẠI LÝ SIM DU LỊCH - Bạn muốn trở thành đại lý sim du lịch của Vinaphone. Hãy để lại thông tin của bạn dưới đây, chúng tôi sẽ liên hệ với bạn sớm nhất. - Họ và Tên * - Email * - Số điện thoại * - Địa chỉ * - Đăng ký - TIN TỨC - hello việt nam - Xem tiếp - Tieu de - Xem tiếp - Khám Phá Những Lợi Ích Vượt Trội Khi Sử Dụng SIM Du Lịch Của VinaPhone - Xem tiếp - Tiêu đề - Xem tiếp - VinaPhone Chính Thức Ra Mắt Dự Án SIM Du Lịch Đáp Ứng Nhu Cầu Của Du Khách Quốc Tế - Xem tiếp - Xem thêm - Theo dõi chúng tôi - VNPT VinaPhone © 2019. - Giấy phép số: 62/GP-TTĐT do Bộ Thông tin - Truyền thông cấp ngày 09/04/2019. - Tập đoàn Bưu chính Viễn thông Việt Nam - Trụ sở: Tòa nhà VNPT, số 57 Phố Huỳnh Thúc Kháng, Phường Láng Hạ, Quận Đống Đa, Thành phố Hà Nội, Việt Nam - Mã số doanh nghiệp: 0100684378 do Sở Kế hoạch và Đầu tư TP.Hà Nội cấp ngày 22/10/2018 - Giấy phép cung cấp dịch vụ viễn thông số 469/GP-BTTTT do Bộ Thông tin và Truyền thông cấp ngày 14/10/2016 - Giấy phép cung cấp dịch vụ viễn thông số 18/GP-CVT do Bộ Thông tin và Truyền thông cấp ngày 18/01/2018</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Ministry of Home Affairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1</v>
+      </c>
+      <c r="B97" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2</v>
+      </c>
+      <c r="B98" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C98" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Ministry of Home Affairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="B99" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2</v>
+      </c>
+      <c r="B100" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C100" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ministry of Home Affairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="B101" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2</v>
+      </c>
+      <c r="B102" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C102" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP - LIÊN HỆ - Vietnamese - TRANG CHỦ - HOÀN THIỆN THÔNG TIN THUÊ BAO - HỖ TRỢ ĐẠI LÝ - CÂU HỎI THƯỜNG GẶP - Mạng di động nhanh nhất Việt Nam, hỗ trợ mạng 5G - Phủ sóng 63/63 tỉnh thành - Liên kết mạng (chuyển vùng quốc tế) với 177 Quốc gia trên khắp thế giới - Data dung lượng lớn, Miễn phí gọi trong nước - Đa dạng lựa chọn với giá cước du lịch hấp dẫn - Hỗ trợ eSim, phát Hotspot cùng nhiều tiện ích khác - HOÀN THIỆN - THÔNG TIN THUÊ BAO - Số thuê bao - Số serial - Hoặc quét - Barcode trên SIM - Xác nhận - CÂU HỎI THƯỜNG GẶP - Chào chưa? - Xin Chào Việt Nam - ĐĂNG KÝ - ĐẠI LÝ SIM DU LỊCH - Bạn muốn trở thành đại lý sim du lịch của Vinaphone. Hãy để lại thông tin của bạn dưới đây, chúng tôi sẽ liên hệ với bạn sớm nhất. - Họ và Tên * - Email * - Số điện thoại * - Địa chỉ * - Đăng ký - TIN TỨC - hello việt nam - Xem tiếp - Tieu de - Xem tiếp - Khám Phá Những Lợi Ích Vượt Trội Khi Sử Dụng SIM Du Lịch Của VinaPhone - Xem tiếp - Tiêu đề - Xem tiếp - VinaPhone Chính Thức Ra Mắt Dự Án SIM Du Lịch Đáp Ứng Nhu Cầu Của Du Khách Quốc Tế - Xem tiếp - Xem thêm - Theo dõi chúng tôi - VNPT VinaPhone © 2019. - Giấy phép số: 62/GP-TTĐT do Bộ Thông tin - Truyền thông cấp ngày 09/04/2019. - Tập đoàn Bưu chính Viễn thông Việt Nam - Trụ sở: Tòa nhà VNPT, số 57 Phố Huỳnh Thúc Kháng, Phường Láng Hạ, Quận Đống Đa, Thành phố Hà Nội, Việt Nam - Mã số doanh nghiệp: 0100684378 do Sở Kế hoạch và Đầu tư TP.Hà Nội cấp ngày 22/10/2018 - Giấy phép cung cấp dịch vụ viễn thông số 469/GP-BTTTT do Bộ Thông tin và Truyền thông cấp ngày 14/10/2016 - Giấy phép cung cấp dịch vụ viễn thông số 18/GP-CVT do Bộ Thông tin và Truyền thông cấp ngày 18/01/2018</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Ministry of Home Affairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="B103" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2</v>
+      </c>
+      <c r="B104" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C104" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1</v>
+      </c>
+      <c r="B105" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2</v>
+      </c>
+      <c r="B106" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C106" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Page.inner_text: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1</v>
+      </c>
+      <c r="B107" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2</v>
+      </c>
+      <c r="B108" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C108" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Page.wait_for_timeout: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>25/10/2023</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>UTC PASIR GUDANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1</v>
+      </c>
+      <c r="B109" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2</v>
+      </c>
+      <c r="B110" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C110" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1</v>
+      </c>
+      <c r="B111" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1</v>
+      </c>
+      <c r="B112" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2</v>
+      </c>
+      <c r="B113" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C113" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Thông tin ekyc không đạt. Vui lòng thử lại!</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1</v>
+      </c>
+      <c r="B114" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2</v>
+      </c>
+      <c r="B115" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C115" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Thông tin ekyc không đạt. Vui lòng thử lại!</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>3</v>
+      </c>
+      <c r="B116" t="n">
+        <v>84832041950</v>
+      </c>
+      <c r="C116" t="n">
+        <v>2228055301</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>ĐĂNG NHẬP - LIÊN HỆ - Vietnamese - TRANG CHỦ - HOÀN THIỆN THÔNG TIN THUÊ BAO - HỖ TRỢ ĐẠI LÝ - CÂU HỎI THƯỜNG GẶP - Mạng di động nhanh nhất Việt Nam, hỗ trợ mạng 5G - Phủ sóng 63/63 tỉnh thành - Liên kết mạng (chuyển vùng quốc tế) với 177 Quốc gia trên khắp thế giới - Data dung lượng lớn, Miễn phí gọi trong nước - Đa dạng lựa chọn với giá cước du lịch hấp dẫn - Hỗ trợ eSim, phát Hotspot cùng nhiều tiện ích khác - Xác nhận thông tin - Quý khách vui lòng kiểm tra lại các thông tin được ghi nhận như sau: - Họ và Tên* - Giới tính* - Ngày sinh* - Quốc tịch* - Số hộ chiếu* - Ngày hết hạn - Ngày cấp - Nơi cấp - Số điện thoại - Thực hiện lạiXác nhận - CÂU HỎI THƯỜNG GẶP - Chào chưa? - Xin Chào Việt Nam - ĐĂNG KÝ - ĐẠI LÝ SIM DU LỊCH - Bạn muốn trở thành đại lý sim du lịch của Vinaphone. Hãy để lại thông tin của bạn dưới đây, chúng tôi sẽ liên hệ với bạn sớm nhất. - Họ và Tên * - Email * - Số điện thoại * - Địa chỉ * - Đăng ký - TIN TỨC - hello việt nam - Xem tiếp - Tieu de - Xem tiếp - Khám Phá Những Lợi Ích Vượt Trội Khi Sử Dụng SIM Du Lịch Của VinaPhone - Xem tiếp - Tiêu đề - Xem tiếp - VinaPhone Chính Thức Ra Mắt Dự Án SIM Du Lịch Đáp Ứng Nhu Cầu Của Du Khách Quốc Tế - Xem tiếp - Xem thêm - Theo dõi chúng tôi - VNPT VinaPhone © 2019. - Giấy phép số: 62/GP-TTĐT do Bộ Thông tin - Truyền thông cấp ngày 09/04/2019. - Tập đoàn Bưu chính Viễn thông Việt Nam - Trụ sở: Tòa nhà VNPT, số 57 Phố Huỳnh Thúc Kháng, Phường Láng Hạ, Quận Đống Đa, Thành phố Hà Nội, Việt Nam - Mã số doanh nghiệp: 0100684378 do Sở Kế hoạch và Đầu tư TP.Hà Nội cấp ngày 22/10/2018 - Giấy phép cung cấp dịch vụ viễn thông số 469/GP-BTTTT do Bộ Thông tin và Truyền thông cấp ngày 14/10/2016 - Giấy phép cung cấp dịch vụ viễn thông số 18/GP-CVT do Bộ Thông tin và Truyền thông cấp ngày 18/01/2018</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1</v>
+      </c>
+      <c r="B117" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>2</v>
+      </c>
+      <c r="B118" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C118" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Thông tin ekyc không đạt. Vui lòng thử lại!</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>3</v>
+      </c>
+      <c r="B119" t="n">
+        <v>84832041950</v>
+      </c>
+      <c r="C119" t="n">
+        <v>2228055301</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1</v>
+      </c>
+      <c r="B120" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>2</v>
+      </c>
+      <c r="B121" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C121" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Thông tin ekyc không đạt. Vui lòng thử lại!</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>3</v>
+      </c>
+      <c r="B122" t="n">
+        <v>84832041950</v>
+      </c>
+      <c r="C122" t="n">
+        <v>2228055301</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>1</v>
+      </c>
+      <c r="B123" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>2</v>
+      </c>
+      <c r="B124" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C124" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>3</v>
+      </c>
+      <c r="B125" t="n">
+        <v>84832041950</v>
+      </c>
+      <c r="C125" t="n">
+        <v>2228055301</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Page.wait_for_timeout: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1</v>
+      </c>
+      <c r="B126" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>2</v>
+      </c>
+      <c r="B127" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C127" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>84832041950</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2228055301</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
         </is>
       </c>
     </row>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4360,20 +4360,14 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>84832041950</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>2228055301</t>
-        </is>
+      <c r="A128" t="n">
+        <v>3</v>
+      </c>
+      <c r="B128" t="n">
+        <v>84832041950</v>
+      </c>
+      <c r="C128" t="n">
+        <v>2228055301</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4391,6 +4385,353 @@
         </is>
       </c>
       <c r="G128" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>1</v>
+      </c>
+      <c r="B129" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Thiếu Ảnh Hộ chiếu</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>1</v>
+      </c>
+      <c r="B130" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Thiếu Ảnh Hộ chiếu</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>1</v>
+      </c>
+      <c r="B131" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Cập nhật thành công (Không có thông báo)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>1</v>
+      </c>
+      <c r="B132" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>1</v>
+      </c>
+      <c r="B133" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>1</v>
+      </c>
+      <c r="B134" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2</v>
+      </c>
+      <c r="B135" t="n">
+        <v>84832041950</v>
+      </c>
+      <c r="C135" t="n">
+        <v>2228055301</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>1</v>
+      </c>
+      <c r="B136" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2</v>
+      </c>
+      <c r="B137" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C137" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Page.wait_for_timeout: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>1</v>
+      </c>
+      <c r="B138" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>84812573457</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2228055418</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Cập nhật thành công (Không có thông báo)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
         <is>
           <t>МВД 02101</t>
         </is>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,20 +550,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>84812573457</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2228055418</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>84812573457</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2228055418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -589,6 +583,198 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="n">
+        <v>84812573457</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2228055418</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Thiếu Ảnh chân dung</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="n">
+        <v>84812573457</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2228055418</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>84832037122</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2228055088</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -739,20 +739,14 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>84832037122</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2228055088</t>
-        </is>
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2228055088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -772,6 +766,356 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Page.wait_for_timeout: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="n">
+        <v>84812573457</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2228055418</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
+Call log:
+  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "domcontentloaded"
+</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="n">
+        <v>84812573457</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2228055418</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>No file input found</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="n">
+        <v>84812573457</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2228055418</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>No file input found</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>84812573457</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2228055418</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
         </is>
       </c>
     </row>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,53 +434,53 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>ngay_cap</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>noi_cap</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>message</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ngay_cap</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>noi_cap</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>814560106</v>
+        <v>84832037122</v>
       </c>
       <c r="C2" t="n">
-        <v>1163972931</v>
+        <v>2228055088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>DUPLICATE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>RANCHI</t>
         </is>
       </c>
     </row>
@@ -496,25 +496,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>18/12/2023</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
-Call log:
-  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "domcontentloaded"
-</t>
+          <t>МВД 02101</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18/12/2023</t>
+          <t>DUPLICATE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>МВД 02101</t>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
         </is>
       </c>
     </row>
@@ -530,118 +527,115 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>DUPLICATE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>RANCHI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>84812573457</v>
+        <v>84832037122</v>
       </c>
       <c r="C5" t="n">
-        <v>2228055418</v>
+        <v>2228055088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>03/02/2024</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
-Call log:
-  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "domcontentloaded"
-</t>
+          <t>MINISTRY OF HOME AFFAIRS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18/12/2023</t>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>МВД 02101</t>
+          <t>Cập nhật thành công (Không có thông báo)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>814560106</v>
+        <v>84812573457</v>
       </c>
       <c r="C6" t="n">
-        <v>1163972931</v>
+        <v>2228055418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DUPLICATE</t>
+          <t>18/12/2023</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+          <t>МВД 02101</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>06/06/2025</t>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>RANCHI</t>
+          <t>Cập nhật thành công (Không có thông báo)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>84812573457</v>
+        <v>814560106</v>
       </c>
       <c r="C7" t="n">
-        <v>2228055418</v>
+        <v>1163972931</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DUPLICATE</t>
+          <t>06/06/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+          <t>RANCHI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18/12/2023</t>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>МВД 02101</t>
+          <t>Cập nhật thành công (Không có thông báo)</t>
         </is>
       </c>
     </row>
@@ -657,465 +651,183 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>03/02/2024</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thiếu Ảnh chân dung</t>
+          <t>MINISTRY OF HOME AFFAIRS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>03/02/2024</t>
+          <t>DUPLICATE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MINISTRY OF HOME AFFAIRS</t>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>814560106</v>
+        <v>84812573457</v>
       </c>
       <c r="C9" t="n">
-        <v>1163972931</v>
+        <v>2228055418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>DUPLICATE</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>RANCHI</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="n">
-        <v>84812573457</v>
+        <v>814560106</v>
       </c>
       <c r="C10" t="n">
-        <v>2228055418</v>
+        <v>1163972931</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>DUPLICATE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>18/12/2023</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>МВД 02101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>84832037122</v>
+        <v>814560106</v>
       </c>
       <c r="C11" t="n">
-        <v>2228055088</v>
+        <v>1163972931</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DUPLICATE</t>
+          <t>06/06/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+          <t>RANCHI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>03/02/2024</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MINISTRY OF HOME AFFAIRS</t>
+          <t>Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="n">
-        <v>814560106</v>
+        <v>84812573457</v>
       </c>
       <c r="C12" t="n">
-        <v>1163972931</v>
+        <v>2228055418</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>FAILED</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>RANCHI</t>
-        </is>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" t="n">
-        <v>84812573457</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2228055418</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>84832037122</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2228055088</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>FAILED</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
-Call log:
-  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "domcontentloaded"
-</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>18/12/2023</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>МВД 02101</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" t="n">
-        <v>814560106</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1163972931</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>RANCHI</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" t="n">
-        <v>84812573457</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2228055418</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>18/12/2023</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>МВД 02101</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" t="n">
-        <v>84832037122</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2228055088</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>03/02/2024</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MINISTRY OF HOME AFFAIRS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" t="n">
-        <v>814560106</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1163972931</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>RANCHI</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B18" t="n">
-        <v>84832037122</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2228055088</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>No file input found</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>03/02/2024</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MINISTRY OF HOME AFFAIRS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" t="n">
-        <v>84812573457</v>
-      </c>
-      <c r="C19" t="n">
-        <v>2228055418</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>No file input found</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>18/12/2023</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>МВД 02101</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" t="n">
-        <v>814560106</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1163972931</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>06/06/2025</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>RANCHI</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>3</v>
-      </c>
-      <c r="B21" t="n">
-        <v>84832037122</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2228055088</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>03/02/2024</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>MINISTRY OF HOME AFFAIRS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>84812573457</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2228055418</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>DUPLICATE</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>18/12/2023</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>МВД 02101</t>
+          <t>Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,20 +795,14 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>84832037122</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2228055088</t>
-        </is>
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2228055088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -828,6 +822,198 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>Page.wait_for_timeout: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" t="n">
+        <v>84812573457</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2228055418</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="n">
+        <v>84812573457</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2228055418</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>814560106</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1163972931</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
         </is>
       </c>
     </row>

--- a/data/result.xlsx
+++ b/data/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,20 +981,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>814560106</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1163972931</t>
-        </is>
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1163972931</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1012,6 +1006,418 @@
         </is>
       </c>
       <c r="G19" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" t="n">
+        <v>84812573457</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2228055418</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="n">
+        <v>84812573457</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2228055418</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Page.wait_for_timeout: Target page, context or browser has been closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Target page, context or browser has been closed
+Call log:
+  - navigating to "https://digishop.vnpt.vn/tourist/", waiting until "domcontentloaded"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" t="n">
+        <v>84812573457</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2228055418</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" t="n">
+        <v>84832037122</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2228055088</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>03/02/2024</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>MINISTRY OF HOME AFFAIRS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
+        <v>814560106</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1163972931</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RANCHI</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>84812573457</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2228055418</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>18/12/2023</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>МВД 02101</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>DUPLICATE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>Thuê bao đã được cập nhật thành công trước đó, hoặc đã vượt quá số lần cập nhật cho phép !</t>
         </is>
